--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039493</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039486</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322966</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322967</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322968</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039487</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763376</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039490</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039491</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039489</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,6 +2201,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2256,6 +2326,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322969</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2371,6 +2446,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2487,6 +2567,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/210541</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429255</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2723,6 +2813,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1323584</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2843,6 +2938,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322963</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2963,6 +3063,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322964</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3083,6 +3188,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763369</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3203,8 +3313,37 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763370</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039488</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135039493</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135039486</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135039492</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>135039487</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135039490</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>135039491</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>135039489</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039488</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135039493</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135039486</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135039492</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>135039487</v>
       </c>
       <c r="B9" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
